--- a/docs/oc-regiones/pasajes-aereos-nacionales/sin-informacion.xlsx
+++ b/docs/oc-regiones/pasajes-aereos-nacionales/sin-informacion.xlsx
@@ -562,7 +562,11 @@
           <t>88.417.000-1</t>
         </is>
       </c>
-      <c r="K2" t="inlineStr"/>
+      <c r="K2" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L2" t="inlineStr">
         <is>
           <t>USD</t>
